--- a/artfynd/A 56271-2021 artfynd.xlsx
+++ b/artfynd/A 56271-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56271-2021 artfynd.xlsx
+++ b/artfynd/A 56271-2021 artfynd.xlsx
@@ -675,53 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13769457</v>
+        <v>96883176</v>
       </c>
       <c r="B2" t="n">
-        <v>42759</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ståltorpet, Ög</t>
+          <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543212.3896747773</v>
+        <v>543172</v>
       </c>
       <c r="R2" t="n">
-        <v>6464359.465577967</v>
+        <v>6464313</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>LST:s källa &amp; kommentar: k16e _NO Ståltorpet</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,31 +759,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl-olof Bergman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96883438</v>
+        <v>96883323</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543204.5388339539</v>
+        <v>543247</v>
       </c>
       <c r="R3" t="n">
-        <v>6464403.507668175</v>
+        <v>6464362</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +844,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,51 +873,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96883600</v>
+        <v>96883355</v>
       </c>
       <c r="B4" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543180.9670733573</v>
+        <v>543249</v>
       </c>
       <c r="R4" t="n">
-        <v>6464393.268217806</v>
+        <v>6464403</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,19 +943,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,51 +972,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96883322</v>
+        <v>96883438</v>
       </c>
       <c r="B5" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543237.232870897</v>
+        <v>543205</v>
       </c>
       <c r="R5" t="n">
-        <v>6464349.756414083</v>
+        <v>6464403</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1094,19 +1042,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,52 +1071,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96883176</v>
+        <v>96883322</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543171.8480590959</v>
+        <v>543237</v>
       </c>
       <c r="R6" t="n">
-        <v>6464312.791655954</v>
+        <v>6464350</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,19 +1140,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,52 +1169,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96883323</v>
+        <v>96883575</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543247.0991926074</v>
+        <v>543178</v>
       </c>
       <c r="R7" t="n">
-        <v>6464361.947358125</v>
+        <v>6464395</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,19 +1238,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,52 +1267,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96883355</v>
+        <v>96883600</v>
       </c>
       <c r="B8" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Risnäs Hagalund, Linköping, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543248.7434108615</v>
+        <v>543181</v>
       </c>
       <c r="R8" t="n">
-        <v>6464403.992141417</v>
+        <v>6464393</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,19 +1336,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,15 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96883575</v>
+        <v>13769457</v>
       </c>
       <c r="B9" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,38 +1376,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Risnäs Hagalund, Linköping, Ög</t>
+          <t>Ståltorpet, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543177.7923443508</v>
+        <v>543212</v>
       </c>
       <c r="R9" t="n">
-        <v>6464394.809459741</v>
+        <v>6464359</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,22 +1430,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>LST:s källa &amp; kommentar: k16e _NO Ståltorpet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,15 +1452,16 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Tommy Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Karl-olof Bergman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1591,12 +1471,7 @@
         <v>96883314</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543242.4838747712</v>
+        <v>543242</v>
       </c>
       <c r="R10" t="n">
-        <v>6464350.864658006</v>
+        <v>6464350</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1663,19 +1538,9 @@
           <t>2021-10-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 56271-2021 artfynd.xlsx
+++ b/artfynd/A 56271-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883323</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883438</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883322</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13769457</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,8 +1609,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96883314</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>